--- a/artfynd/A 25870-2025 artfynd.xlsx
+++ b/artfynd/A 25870-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,47 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123325532</v>
+        <v>123325543</v>
       </c>
       <c r="B2" t="n">
-        <v>98100</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600478</v>
+        <v>600539</v>
       </c>
       <c r="R2" t="n">
-        <v>6974370</v>
+        <v>6974431</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1448</t>
+          <t>2024_1442</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Sumpskog</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,59 +805,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123325541</v>
+        <v>131106814</v>
       </c>
       <c r="B3" t="n">
-        <v>98100</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nordansjön, Mpd</t>
+          <t>Paljack, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600516</v>
+        <v>600517</v>
       </c>
       <c r="R3" t="n">
-        <v>6974406</v>
+        <v>6974472</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,32 +879,27 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1443</t>
+          <t>2025_0363</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Sumpskog</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,7 +919,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -945,59 +930,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325543</v>
+        <v>131106812</v>
       </c>
       <c r="B4" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nordansjön, Mpd</t>
+          <t>Paljack, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600539</v>
+        <v>600509</v>
       </c>
       <c r="R4" t="n">
-        <v>6974431</v>
+        <v>6974463</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,32 +1004,27 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1442</t>
+          <t>2025_0365</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>sälg</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1069,10 +1044,395 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123325532</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nordansjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>600478</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6974370</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2024_1448</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Sumpskog</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
           <t>Douglas Skarp</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123325541</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nordansjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>600516</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6974406</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2024_1443</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Sumpskog</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Douglas Skarp</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131106813</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Paljack, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>600498</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6974468</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2025_0364</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>David Isaksson, Anders Forsberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>

--- a/artfynd/A 25870-2025 artfynd.xlsx
+++ b/artfynd/A 25870-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325543</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -927,6 +937,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106814</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1052,6 +1067,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106812</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1182,6 +1202,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325532</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1312,6 +1337,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325541</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1437,8 +1467,21 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106813</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>